--- a/stories/arbres/ATOM-REL.MOQ.004-03.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.004-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Quentin est dans la cuisine avec maman. Rosa est là aussi. Rosa a un peu de farine sur le nez. Ça sent le gâteau. Quentin voit le téléphone de maman. Il a une idée de photo. Quentin dit : je peux prendre une photo ? Maman dit : on doit demander. Demander, c'est parler avant. Une photo se fait avec un adulte. Maman dit : le téléphone reste avec l'adulte. On ne prend pas une photo pour rire de l'autre. Ce n'est pas pour rire de l'autre. Quentin dit : d'accord. Rosa essuie son nez. Maman prend la photo. Quentin et Rosa sourient. Le téléphone reste dans la main de maman. Quentin dit merci.</t>
+          <t>Quentin est dans la cuisine avec maman. Rosa est là aussi. Rosa a un peu de farine sur le nez. Ça sent le gâteau. Quentin voit le téléphone de maman. Il a une idée de photo. Je peux prendre une photo ? On doit demander. Demander, c'est parler avant. Une photo se fait avec un adulte. Le téléphone reste avec l'adulte. On ne prend pas une photo pour rire de l'autre. Ce n'est pas pour rire de l'autre. D'accord. Rosa essuie son nez. Maman prend la photo. Quentin et Rosa sourient. Le téléphone reste dans la main de maman. Quentin dit merci.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Quentin est dans la cuisine avec maman. Rosa est là aussi. Rosa a un peu de farine sur le nez. Ça sent le gâteau. Quentin voit le téléphone de maman. Il a une idée de photo.
+enfant-m|Je peux prendre une photo ?
+maman|On doit demander. Demander, c'est parler avant.
+narrateur|Une photo se fait avec un adulte.
+maman|Le téléphone reste avec l'adulte. On ne prend pas une photo pour rire de l'autre. Ce n'est pas pour rire de l'autre.
+enfant-m|D'accord.
+narrateur|Rosa essuie son nez. Maman prend la photo. Quentin et Rosa sourient. Le téléphone reste dans la main de maman. Quentin dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Quentin veut une photo. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Quentin a su demander. Le téléphone reste avec l'adulte. Ce n'est pas pour rire de l'autre.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1828,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Quentin et Rosa rangent le saladier. Maman glisse le téléphone.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1995,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.004-03.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.004-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Rosa essuie son nez. Maman prend la photo. Quentin et Rosa sourient. Le téléphone reste dans la main de maman. Quentin dit merci.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Quentin veut une photo. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1677,7 @@
           <t>narrateur|Quentin a su demander. Le téléphone reste avec l'adulte. Ce n'est pas pour rire de l'autre.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1841,7 @@
           <t>narrateur|Quentin et Rosa rangent le saladier. Maman glisse le téléphone.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2052,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2267,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.MOQ.004-03.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.004-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Quentin demande avant la photo</t>
+          <t>Raphaël demande avant la photo</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Dans la cuisine à la vanille, Raphaël veut une photo de Mila. Il demande. Le téléphone reste avec maman. Ce n'est pas pour rire de l'autre. Puis ils demandent encore pour le gâteau.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Quentin est dans la cuisine avec maman. Rosa est là aussi. Rosa a un peu de farine sur le nez. Ça sent le gâteau. Quentin voit le téléphone de maman. Il a une idée de photo. Je peux prendre une photo ? On doit demander. Demander, c'est parler avant. Une photo se fait avec un adulte. Le téléphone reste avec l'adulte. On ne prend pas une photo pour rire de l'autre. Ce n'est pas pour rire de l'autre. D'accord. Rosa essuie son nez. Maman prend la photo. Quentin et Rosa sourient. Le téléphone reste dans la main de maman. Quentin dit merci.</t>
+          <t>La vitre de la cuisine est toute embuée. La vapeur sent la vanille chaude. Une cuillère en bois tape le saladier jaune. La farine fait un petit nuage blanc. Le plancher est un peu collant sous les chaussettes. Une miette sucrée brille près du pot. Tu entends le four, Raphaël ? Il fait un petit bruit. Oui. Il chauffe le gâteau. En ce moment, Raphaël mélange la pâte. La pâte est épaisse et douce. Mila est là, tout près du saladier. Mila a de la farine sur le nez. Ça fait un petit point blanc. Mila, tu as de la farine. Mila se touche le nez. Elle rit un peu. Raphaël voit le téléphone de maman. Le téléphone est sur la table. Il est loin de la pâte. Je peux prendre une photo ? On doit demander. Demander, c'est parler avant. Une photo se fait avec un adulte. Le téléphone reste avec l'adulte. Ce n'est pas pour rire de l'autre. D'accord. Raphaël se tourne vers Mila. Mila, on peut ? Mila dit oui. Mila essuie son nez. Bravo, Raphaël. Tu as demandé. Tu as fait du bon travail. Maman prend le téléphone. Le téléphone reste dans sa main. Maman prend la photo. Raphaël et Mila sourient. Merci, maman. De rien. Le saladier brille encore. Le gâteau sent plus fort. Et le gâteau ? On peut une photo du gâteau ? On demande encore. Le téléphone reste avec moi. On peut, maman ? Oui. Maman photographie le gâteau doré. Ce n'est pas pour rire de l'autre. C'est pour garder le moment. Tu as demandé deux fois. Bravo. Le téléphone est avec toi. Oui. Avec l'adulte. Ils lèchent un peu de pâte. C'est sucré et doux. Tu as fini de mélanger ? Oui, maman. Le four continue son petit bruit. La fenêtre reste embuée. Raphaël dessine un petit rond dans la buée. Un rond, c'est joli. Mila dessine un soleil à côté. Vous avez demandé avant la photo. C'est le bon geste. On demande. L'adulte a le téléphone. Oui. Pas pour rire de l'autre. Le gâteau cuit tout doucement. La cuisine est chaude et douce. Mila pose sa joue sur la table. Le bois est un peu collant. Tu veux un verre d'eau ? Oui, maman. L'eau est fraîche. Elle fait un petit cloc dans le verre. On a demandé avant la photo. Et le téléphone est avec toi. Oui. Une goutte de vanille brille sur la cuillère. Mila la montre du doigt. C'est sucré. Oui. On goûtera le gâteau plus tard. Le four fait toujours son petit bruit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1324,102 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Quentin est dans la cuisine avec maman. Rosa est là aussi. Rosa a un peu de farine sur le nez. Ça sent le gâteau. Quentin voit le téléphone de maman. Il a une idée de photo.
+          <t>narrateur|La vitre de la cuisine est toute embuée.
+narrateur|La vapeur sent la vanille chaude.
+narrateur|Une cuillère en bois tape le saladier jaune.
+narrateur|La farine fait un petit nuage blanc.
+narrateur|Le plancher est un peu collant sous les chaussettes.
+narrateur|Une miette sucrée brille près du pot.
+maman|Tu entends le four, Raphaël ?
+enfant-m|Il fait un petit bruit.
+maman|Oui.
+maman|Il chauffe le gâteau.
+narrateur|En ce moment, Raphaël mélange la pâte.
+narrateur|La pâte est épaisse et douce.
+narrateur|Mila est là, tout près du saladier.
+narrateur|Mila a de la farine sur le nez.
+narrateur|Ça fait un petit point blanc.
+enfant-m|Mila, tu as de la farine.
+narrateur|Mila se touche le nez.
+narrateur|Elle rit un peu.
+narrateur|Raphaël voit le téléphone de maman.
+narrateur|Le téléphone est sur la table.
+narrateur|Il est loin de la pâte.
 enfant-m|Je peux prendre une photo ?
-maman|On doit demander. Demander, c'est parler avant.
-narrateur|Une photo se fait avec un adulte.
-maman|Le téléphone reste avec l'adulte. On ne prend pas une photo pour rire de l'autre. Ce n'est pas pour rire de l'autre.
+maman|On doit demander.
+maman|Demander, c'est parler avant.
+maman|Une photo se fait avec un adulte.
+maman|Le téléphone reste avec l'adulte.
+maman|Ce n'est pas pour rire de l'autre.
 enfant-m|D'accord.
-narrateur|Rosa essuie son nez. Maman prend la photo. Quentin et Rosa sourient. Le téléphone reste dans la main de maman. Quentin dit merci.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+narrateur|Raphaël se tourne vers Mila.
+enfant-m|Mila, on peut ?
+narrateur|Mila dit oui.
+narrateur|Mila essuie son nez.
+maman|Bravo, Raphaël.
+maman|Tu as demandé.
+maman|Tu as fait du bon travail.
+narrateur|Maman prend le téléphone.
+narrateur|Le téléphone reste dans sa main.
+narrateur|Maman prend la photo.
+narrateur|Raphaël et Mila sourient.
+enfant-m|Merci, maman.
+maman|De rien.
+narrateur|Le saladier brille encore.
+narrateur|Le gâteau sent plus fort.
+enfant-m|Et le gâteau ?
+enfant-m|On peut une photo du gâteau ?
+maman|On demande encore.
+maman|Le téléphone reste avec moi.
+enfant-m|On peut, maman ?
+maman|Oui.
+narrateur|Maman photographie le gâteau doré.
+narrateur|Ce n'est pas pour rire de l'autre.
+narrateur|C'est pour garder le moment.
+maman|Tu as demandé deux fois.
+maman|Bravo.
+enfant-m|Le téléphone est avec toi.
+maman|Oui.
+maman|Avec l'adulte.
+narrateur|Ils lèchent un peu de pâte.
+narrateur|C'est sucré et doux.
+maman|Tu as fini de mélanger ?
+enfant-m|Oui, maman.
+narrateur|Le four continue son petit bruit.
+narrateur|La fenêtre reste embuée.
+narrateur|Raphaël dessine un petit rond dans la buée.
+maman|Un rond, c'est joli.
+narrateur|Mila dessine un soleil à côté.
+maman|Vous avez demandé avant la photo.
+maman|C'est le bon geste.
+enfant-m|On demande.
+enfant-m|L'adulte a le téléphone.
+maman|Oui.
+maman|Pas pour rire de l'autre.
+narrateur|Le gâteau cuit tout doucement.
+narrateur|La cuisine est chaude et douce.
+narrateur|Mila pose sa joue sur la table.
+narrateur|Le bois est un peu collant.
+maman|Tu veux un verre d'eau ?
+enfant-m|Oui, maman.
+narrateur|L'eau est fraîche.
+narrateur|Elle fait un petit cloc dans le verre.
+maman|On a demandé avant la photo.
+enfant-m|Et le téléphone est avec toi.
+maman|Oui.
+narrateur|Une goutte de vanille brille sur la cuillère.
+narrateur|Mila la montre du doigt.
+enfant-m|C'est sucré.
+maman|Oui.
+maman|On goûtera le gâteau plus tard.
+narrateur|Le four fait toujours son petit bruit.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>cuillere_saladier</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1346,7 +1444,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Quentin veut une photo. Que fait-il ?</t>
+          <t>Raphaël veut une photo. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1600,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Quentin veut une photo. Que fait-il ?</t>
+          <t>narrateur|Raphaël veut une photo.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1629,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Quentin a su demander. Le téléphone reste avec l'adulte. Ce n'est pas pour rire de l'autre.</t>
+          <t>Raphaël a su demander. Le téléphone reste avec l'adulte. Ce n'est pas pour rire de l'autre. Bravo, Raphaël. Tu as fait du bon travail. J'ai demandé. Le téléphone est avec toi. Oui. Avec l'adulte. On demande avant une photo.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1674,7 +1773,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Quentin a su demander. Le téléphone reste avec l'adulte. Ce n'est pas pour rire de l'autre.</t>
+          <t>narrateur|Raphaël a su demander.
+narrateur|Le téléphone reste avec l'adulte.
+narrateur|Ce n'est pas pour rire de l'autre.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+enfant-m|J'ai demandé.
+enfant-m|Le téléphone est avec toi.
+maman|Oui.
+maman|Avec l'adulte.
+maman|On demande avant une photo.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1702,7 +1810,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Quentin et Rosa rangent le saladier. Maman glisse le téléphone.</t>
+          <t>Raphaël et Mila rangent le saladier. La cuillère tapote encore un peu. Tu glisses le saladier ici ? Oui, maman. Maman range le téléphone. Il n'est plus sur la table. On attend le gâteau, maintenant. Il sent bon. Oui. Tu as demandé. C'était le bon geste. La buée part tout doucement. Un rond reste sur la vitre.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1838,7 +1946,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Quentin et Rosa rangent le saladier. Maman glisse le téléphone.</t>
+          <t>narrateur|Raphaël et Mila rangent le saladier.
+narrateur|La cuillère tapote encore un peu.
+maman|Tu glisses le saladier ici ?
+enfant-m|Oui, maman.
+narrateur|Maman range le téléphone.
+narrateur|Il n'est plus sur la table.
+maman|On attend le gâteau, maintenant.
+enfant-m|Il sent bon.
+maman|Oui.
+maman|Tu as demandé.
+maman|C'était le bon geste.
+narrateur|La buée part tout doucement.
+narrateur|Un rond reste sur la vitre.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1866,7 +1986,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a demandé. Le téléphone est avec maman. Bravo. Tu as fait du bon travail. Le gâteau cuit encore. La cuisine sent la vanille. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2006,7 +2126,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a demandé.
+enfant-m|Le téléphone est avec maman.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Le gâteau cuit encore.
+narrateur|La cuisine sent la vanille.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2028,7 +2154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2066,6 +2192,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.004-03.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.004-03.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La vitre de la cuisine est toute embuée. La vapeur sent la vanille chaude. Une cuillère en bois tape le saladier jaune. La farine fait un petit nuage blanc. Le plancher est un peu collant sous les chaussettes. Une miette sucrée brille près du pot. Tu entends le four, Raphaël ? Il fait un petit bruit. Oui. Il chauffe le gâteau. En ce moment, Raphaël mélange la pâte. La pâte est épaisse et douce. Mila est là, tout près du saladier. Mila a de la farine sur le nez. Ça fait un petit point blanc. Mila, tu as de la farine. Mila se touche le nez. Elle rit un peu. Raphaël voit le téléphone de maman. Le téléphone est sur la table. Il est loin de la pâte. Je peux prendre une photo ? On doit demander. Demander, c'est parler avant. Une photo se fait avec un adulte. Le téléphone reste avec l'adulte. Ce n'est pas pour rire de l'autre. D'accord. Raphaël se tourne vers Mila. Mila, on peut ? Mila dit oui. Mila essuie son nez. Bravo, Raphaël. Tu as demandé. Tu as fait du bon travail. Maman prend le téléphone. Le téléphone reste dans sa main. Maman prend la photo. Raphaël et Mila sourient. Merci, maman. De rien. Le saladier brille encore. Le gâteau sent plus fort. Et le gâteau ? On peut une photo du gâteau ? On demande encore. Le téléphone reste avec moi. On peut, maman ? Oui. Maman photographie le gâteau doré. Ce n'est pas pour rire de l'autre. C'est pour garder le moment. Tu as demandé deux fois. Bravo. Le téléphone est avec toi. Oui. Avec l'adulte. Ils lèchent un peu de pâte. C'est sucré et doux. Tu as fini de mélanger ? Oui, maman. Le four continue son petit bruit. La fenêtre reste embuée. Raphaël dessine un petit rond dans la buée. Un rond, c'est joli. Mila dessine un soleil à côté. Vous avez demandé avant la photo. C'est le bon geste. On demande. L'adulte a le téléphone. Oui. Pas pour rire de l'autre. Le gâteau cuit tout doucement. La cuisine est chaude et douce. Mila pose sa joue sur la table. Le bois est un peu collant. Tu veux un verre d'eau ? Oui, maman. L'eau est fraîche. Elle fait un petit cloc dans le verre. On a demandé avant la photo. Et le téléphone est avec toi. Oui. Une goutte de vanille brille sur la cuillère. Mila la montre du doigt. C'est sucré. Oui. On goûtera le gâteau plus tard. Le four fait toujours son petit bruit.</t>
+          <t>La vitre de la cuisine est toute embuée. La vapeur sent la vanille chaude. Une cuillère en bois tape le saladier jaune. La farine fait un petit nuage blanc. Le plancher est un peu collant sous les chaussettes. Une miette sucrée brille près du pot. Tu entends le four, Raphaël ? Il fait un petit bruit. Oui. Il chauffe le gâteau. En ce moment, Raphaël mélange la pâte. La pâte est épaisse et douce. Mila est là, tout près du saladier. Mila a de la farine sur le nez. Ça fait un petit point blanc. Mila, tu as de la farine. Mila se touche le nez. Elle rit un peu. Raphaël voit le téléphone de maman. Le téléphone est sur la table. Il est loin de la pâte. Je peux prendre une photo ? On doit demander. Demander, c'est parler avant. Une photo se fait avec un adulte. Le téléphone reste avec l'adulte. Ce n'est pas pour rire de l'autre. D'accord. Raphaël se tourne vers Mila. Mila, on peut ? Mila dit oui. Mila essuie son nez. Bravo, Raphaël. Tu as demandé. Maman prend le téléphone. Le téléphone reste dans sa main. Maman prend la photo. Raphaël et Mila sourient. Merci, maman. De rien. Le saladier brille encore. Le gâteau sent plus fort. Et le gâteau ? On peut une photo du gâteau ? On demande encore. Le téléphone reste avec moi. On peut, maman ? Oui. Maman photographie le gâteau doré. Ce n'est pas pour rire de l'autre. C'est pour garder le moment. Tu as demandé deux fois. Bravo. Le téléphone est avec toi. Oui. Avec l'adulte. Ils lèchent un peu de pâte. C'est sucré et doux. Tu as fini de mélanger ? Oui, maman. Le four continue son petit bruit. La fenêtre reste embuée. Raphaël dessine un petit rond dans la buée. Un rond, c'est joli. Mila dessine un soleil à côté. Vous avez demandé avant la photo. C'est le bon geste. On demande. L'adulte a le téléphone. Oui. Pas pour rire de l'autre. Le gâteau cuit tout doucement. La cuisine est chaude et douce. Mila pose sa joue sur la table. Le bois est un peu collant. Tu veux un verre d'eau ? Oui, maman. L'eau est fraîche. Elle fait un petit cloc dans le verre. On a demandé avant la photo. Et le téléphone est avec toi. Oui. Une goutte de vanille brille sur la cuillère. Mila la montre du doigt. C'est sucré. Oui. On goûtera le gâteau plus tard. Le four fait toujours son petit bruit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Quentin est dans la cuisine avec maman. Rosa est là aussi. Rosa a un peu de farine sur le nez. Ça sent le gâteau. Quentin voit le téléphone de maman. Il a une idée de photo. Quentin dit : je peux prendre une photo ? Maman dit : on doit &lt;emphasis level="moderate"&gt;demander&lt;/emphasis&gt;. Demander, c'est parler avant. Une photo se fait avec un adulte. Maman dit : le téléphone reste avec l'adulte. On ne prend pas une photo pour rire de l'autre. Ce n'est pas pour rire de l'autre. Quentin dit : d'accord. Rosa essuie son nez. Maman prend la photo. Quentin et Rosa sourient. Le téléphone reste dans la main de maman. Quentin dit merci.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La vitre de la cuisine est toute embuée. La vapeur sent la vanille chaude. Une cuillère en bois tape le saladier jaune. La farine fait un petit nuage blanc. Le plancher est un peu collant sous les chaussettes. Une miette sucrée brille près du pot. Tu entends le four, Raphaël ? Il fait un petit bruit. Oui. Il chauffe le gâteau. En ce moment, Raphaël mélange la pâte. La pâte est épaisse et douce. Mila est là, tout près du saladier. Mila a de la farine sur le nez. Ça fait un petit point blanc. Mila, tu as de la farine. Mila se touche le nez. Elle rit un peu. Raphaël voit le téléphone de maman. Le téléphone est sur la table. Il est loin de la pâte. Je peux prendre une photo ? On doit demander. Demander, c'est parler avant. Une photo se fait avec un adulte. Le téléphone reste avec l'adulte. Ce n'est pas pour rire de l'autre. D'accord. Raphaël se tourne vers Mila. Mila, on peut ? Mila dit oui. Mila essuie son nez. Bravo, Raphaël. Tu as demandé. Maman prend le téléphone. Le téléphone reste dans sa main. Maman prend la photo. Raphaël et Mila sourient. Merci, maman. De rien. Le saladier brille encore. Le gâteau sent plus fort. Et le gâteau ? On peut une photo du gâteau ? On demande encore. Le téléphone reste avec moi. On peut, maman ? Oui. Maman photographie le gâteau doré. Ce n'est pas pour rire de l'autre. C'est pour garder le moment. Tu as demandé deux fois. Bravo. Le téléphone est avec toi. Oui. Avec l'adulte. Ils lèchent un peu de pâte. C'est sucré et doux. Tu as fini de mélanger ? Oui, maman. Le four continue son petit bruit. La fenêtre reste embuée. Raphaël dessine un petit rond dans la buée. Un rond, c'est joli. Mila dessine un soleil à côté. Vous avez demandé avant la photo. C'est le bon geste. On demande. L'adulte a le téléphone. Oui. Pas pour rire de l'autre. Le gâteau cuit tout doucement. La cuisine est chaude et douce. Mila pose sa joue sur la table. Le bois est un peu collant. Tu veux un verre d'eau ? Oui, maman. L'eau est fraîche. Elle fait un petit cloc dans le verre. On a demandé avant la photo. Et le téléphone est avec toi. Oui. Une goutte de vanille brille sur la cuillère. Mila la montre du doigt. C'est sucré. Oui. On goûtera le gâteau plus tard. Le four fait toujours son petit bruit.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1358,7 +1358,6 @@
 narrateur|Mila essuie son nez.
 maman|Bravo, Raphaël.
 maman|Tu as demandé.
-maman|Tu as fait du bon travail.
 narrateur|Maman prend le téléphone.
 narrateur|Le téléphone reste dans sa main.
 narrateur|Maman prend la photo.
@@ -1449,7 +1448,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Quentin veut une photo. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël veut une photo. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1604,7 +1603,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1629,12 +1627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a su demander. Le téléphone reste avec l'adulte. Ce n'est pas pour rire de l'autre. Bravo, Raphaël. Tu as fait du bon travail. J'ai demandé. Le téléphone est avec toi. Oui. Avec l'adulte. On demande avant une photo.</t>
+          <t>Raphaël a su demander. Le téléphone reste avec l'adulte. Ce n'est pas pour rire de l'autre. Bravo, Raphaël. J'ai demandé. Le téléphone est avec toi. Oui. Avec l'adulte. On demande avant une photo.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Quentin a su &lt;emphasis level="moderate"&gt;demander&lt;/emphasis&gt;. Le téléphone reste avec l'adulte. Ce n'est pas pour rire de l'autre.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël a su demander. Le téléphone reste avec l'adulte. Ce n'est pas pour rire de l'autre. Bravo, Raphaël. J'ai demandé. Le téléphone est avec toi. Oui. Avec l'adulte. On demande avant une photo.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1777,7 +1775,6 @@
 narrateur|Le téléphone reste avec l'adulte.
 narrateur|Ce n'est pas pour rire de l'autre.
 maman|Bravo, Raphaël.
-maman|Tu as fait du bon travail.
 enfant-m|J'ai demandé.
 enfant-m|Le téléphone est avec toi.
 maman|Oui.
@@ -1785,7 +1782,6 @@
 maman|On demande avant une photo.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1815,7 +1811,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Quentin et Rosa rangent le saladier. Maman glisse le téléphone.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël et Mila rangent le saladier. La cuillère tapote encore un peu. Tu glisses le saladier ici ? Oui, maman. Maman range le téléphone. Il n'est plus sur la table. On attend le gâteau, maintenant. Il sent bon. Oui. Tu as demandé. C'était le bon geste. La buée part tout doucement. Un rond reste sur la vitre.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1961,7 +1957,6 @@
 narrateur|Un rond reste sur la vitre.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1986,12 +1981,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>On a demandé. Le téléphone est avec maman. Bravo. Tu as fait du bon travail. Le gâteau cuit encore. La cuisine sent la vanille. L'histoire est finie.</t>
+          <t>On a demandé. Le téléphone est avec maman. Bravo. Le gâteau cuit encore. La cuisine sent la vanille.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>On a demandé. Le téléphone est avec maman. Bravo. Le gâteau cuit encore. La cuisine sent la vanille.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2129,13 +2124,10 @@
           <t>enfant-m|On a demandé.
 enfant-m|Le téléphone est avec maman.
 maman|Bravo.
-maman|Tu as fait du bon travail.
 narrateur|Le gâteau cuit encore.
-narrateur|La cuisine sent la vanille.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La cuisine sent la vanille.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2154,7 +2146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2199,6 +2191,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.004-03.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.004-03.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Quentin, maman, Rosa</t>
+          <t>Raphaël, Mila, maman</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.004-03.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.004-03.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Raphaël demande avant la photo</t>
+          <t>La farine sur le nez</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cuisine</t>
+          <t>cuisine, buée, saladier, four</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Dans la cuisine à la vanille, Raphaël veut une photo de Mila. Il demande. Le téléphone reste avec maman. Ce n'est pas pour rire de l'autre. Puis ils demandent encore pour le gâteau.</t>
+          <t>Raphaël veut un souvenir de la farine sur le nez de Mila. Il avance la main vers le téléphone. Maman attend. Il parle. Alors la photo. Le gâteau sort. Il parle encore. Ils lèchent la cuillère.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La vitre de la cuisine est toute embuée. La vapeur sent la vanille chaude. Une cuillère en bois tape le saladier jaune. La farine fait un petit nuage blanc. Le plancher est un peu collant sous les chaussettes. Une miette sucrée brille près du pot. Tu entends le four, Raphaël ? Il fait un petit bruit. Oui. Il chauffe le gâteau. En ce moment, Raphaël mélange la pâte. La pâte est épaisse et douce. Mila est là, tout près du saladier. Mila a de la farine sur le nez. Ça fait un petit point blanc. Mila, tu as de la farine. Mila se touche le nez. Elle rit un peu. Raphaël voit le téléphone de maman. Le téléphone est sur la table. Il est loin de la pâte. Je peux prendre une photo ? On doit demander. Demander, c'est parler avant. Une photo se fait avec un adulte. Le téléphone reste avec l'adulte. Ce n'est pas pour rire de l'autre. D'accord. Raphaël se tourne vers Mila. Mila, on peut ? Mila dit oui. Mila essuie son nez. Bravo, Raphaël. Tu as demandé. Maman prend le téléphone. Le téléphone reste dans sa main. Maman prend la photo. Raphaël et Mila sourient. Merci, maman. De rien. Le saladier brille encore. Le gâteau sent plus fort. Et le gâteau ? On peut une photo du gâteau ? On demande encore. Le téléphone reste avec moi. On peut, maman ? Oui. Maman photographie le gâteau doré. Ce n'est pas pour rire de l'autre. C'est pour garder le moment. Tu as demandé deux fois. Bravo. Le téléphone est avec toi. Oui. Avec l'adulte. Ils lèchent un peu de pâte. C'est sucré et doux. Tu as fini de mélanger ? Oui, maman. Le four continue son petit bruit. La fenêtre reste embuée. Raphaël dessine un petit rond dans la buée. Un rond, c'est joli. Mila dessine un soleil à côté. Vous avez demandé avant la photo. C'est le bon geste. On demande. L'adulte a le téléphone. Oui. Pas pour rire de l'autre. Le gâteau cuit tout doucement. La cuisine est chaude et douce. Mila pose sa joue sur la table. Le bois est un peu collant. Tu veux un verre d'eau ? Oui, maman. L'eau est fraîche. Elle fait un petit cloc dans le verre. On a demandé avant la photo. Et le téléphone est avec toi. Oui. Une goutte de vanille brille sur la cuillère. Mila la montre du doigt. C'est sucré. Oui. On goûtera le gâteau plus tard. Le four fait toujours son petit bruit.</t>
+          <t>La vitre de la cuisine est toute embuée. La vapeur sent la vanille chaude. Une cuillère en bois tape le saladier jaune. La farine fait un petit nuage blanc. Le plancher est un peu collant sous les chaussettes. Une miette sucrée brille près du pot. Tu entends le four, Raphaël ? Il fait un petit bruit. Oui. Il chauffe le gâteau. En ce moment, Raphaël mélange la pâte. La pâte est épaisse et douce. Mila est là, tout près du saladier. Mila a de la farine sur le nez. Ça fait un petit point blanc. Mila, tu as de la farine. Mila se touche le nez. Elle rit un peu. Je veux un souvenir. Raphaël voit le téléphone de maman. Le téléphone est sur la table. Il est loin de la pâte. Raphaël avance la main. Maman ne bouge pas. Maman attend, tout près. Raphaël pose sa main. Maman, je peux demander une photo ? Oui. Raphaël se tourne vers Mila. Mila, on peut ? Oui. Mila essuie un peu son nez. Un point blanc reste. Maman prend le téléphone. Le téléphone reste dans sa main. Maman prend la photo. Raphaël et Mila sourient. Merci, maman. Bravo, Raphaël. Le saladier brille encore. Le gâteau sent plus fort. Plus tard, le four s'ouvre. Le gâteau est doré, tout chaud. Et le gâteau ? Un souvenir du gâteau ? Raphaël avance encore la main. Maman attend encore. On peut, maman ? Oui. Maman photographie le gâteau doré. Le téléphone reste avec elle. Le téléphone est avec toi. Oui. Ils lèchent un peu de pâte. C'est sucré et doux. Tu as fini de mélanger ? Oui, maman. Le four continue son petit bruit. La fenêtre reste embuée. Raphaël dessine un petit rond dans la buée. Un rond, c'est joli. Mila dessine un soleil à côté. On a le souvenir. Oui. Le gâteau cuit tout doucement. La cuisine est chaude et douce. Mila pose sa joue sur la table. Le bois est un peu collant. Tu veux un verre d'eau ? Oui, maman. L'eau est fraîche. Elle fait un petit cloc dans le verre. Et le téléphone est avec toi. Oui. Une goutte de vanille brille sur la cuillère. Mila la montre du doigt. C'est sucré. Oui. On goûtera le gâteau plus tard. Le four fait toujours son petit bruit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>La vitre de la cuisine est toute embuée. La vapeur sent la vanille chaude. Une cuillère en bois tape le saladier jaune. La farine fait un petit nuage blanc. Le plancher est un peu collant sous les chaussettes. Une miette sucrée brille près du pot. Tu entends le four, Raphaël ? Il fait un petit bruit. Oui. Il chauffe le gâteau. En ce moment, Raphaël mélange la pâte. La pâte est épaisse et douce. Mila est là, tout près du saladier. Mila a de la farine sur le nez. Ça fait un petit point blanc. Mila, tu as de la farine. Mila se touche le nez. Elle rit un peu. Raphaël voit le téléphone de maman. Le téléphone est sur la table. Il est loin de la pâte. Je peux prendre une photo ? On doit demander. Demander, c'est parler avant. Une photo se fait avec un adulte. Le téléphone reste avec l'adulte. Ce n'est pas pour rire de l'autre. D'accord. Raphaël se tourne vers Mila. Mila, on peut ? Mila dit oui. Mila essuie son nez. Bravo, Raphaël. Tu as demandé. Maman prend le téléphone. Le téléphone reste dans sa main. Maman prend la photo. Raphaël et Mila sourient. Merci, maman. De rien. Le saladier brille encore. Le gâteau sent plus fort. Et le gâteau ? On peut une photo du gâteau ? On demande encore. Le téléphone reste avec moi. On peut, maman ? Oui. Maman photographie le gâteau doré. Ce n'est pas pour rire de l'autre. C'est pour garder le moment. Tu as demandé deux fois. Bravo. Le téléphone est avec toi. Oui. Avec l'adulte. Ils lèchent un peu de pâte. C'est sucré et doux. Tu as fini de mélanger ? Oui, maman. Le four continue son petit bruit. La fenêtre reste embuée. Raphaël dessine un petit rond dans la buée. Un rond, c'est joli. Mila dessine un soleil à côté. Vous avez demandé avant la photo. C'est le bon geste. On demande. L'adulte a le téléphone. Oui. Pas pour rire de l'autre. Le gâteau cuit tout doucement. La cuisine est chaude et douce. Mila pose sa joue sur la table. Le bois est un peu collant. Tu veux un verre d'eau ? Oui, maman. L'eau est fraîche. Elle fait un petit cloc dans le verre. On a demandé avant la photo. Et le téléphone est avec toi. Oui. Une goutte de vanille brille sur la cuillère. Mila la montre du doigt. C'est sucré. Oui. On goûtera le gâteau plus tard. Le four fait toujours son petit bruit.</t>
+          <t>La vitre de la cuisine est toute embuée. La vapeur sent la vanille chaude. Une cuillère en bois tape le saladier jaune. La farine fait un petit nuage blanc. Le plancher est un peu collant sous les chaussettes. Une miette sucrée brille près du pot. Tu entends le four, Raphaël ? Il fait un petit bruit. Oui. Il chauffe le gâteau. En ce moment, Raphaël mélange la pâte. La pâte est épaisse et douce. Mila est là, tout près du saladier. Mila a de la farine sur le nez. Ça fait un petit point blanc. Mila, tu as de la farine. Mila se touche le nez. Elle rit un peu. Je veux un souvenir. Raphaël voit le téléphone de maman. Le téléphone est sur la table. Il est loin de la pâte. Raphaël avance la main. Maman ne bouge pas. Maman attend, tout près. Raphaël pose sa main. Maman, je peux demander une photo ? Oui. Raphaël se tourne vers Mila. Mila, on peut ? Oui. Mila essuie un peu son nez. Un point blanc reste. Maman prend le téléphone. Le téléphone reste dans sa main. Maman prend la photo. Raphaël et Mila sourient. Merci, maman. Bravo, Raphaël. Le saladier brille encore. Le gâteau sent plus fort. Plus tard, le four s'ouvre. Le gâteau est doré, tout chaud. Et le gâteau ? Un souvenir du gâteau ? Raphaël avance encore la main. Maman attend encore. On peut, maman ? Oui. Maman photographie le gâteau doré. Le téléphone reste avec elle. Le téléphone est avec toi. Oui. Ils lèchent un peu de pâte. C'est sucré et doux. Tu as fini de mélanger ? Oui, maman. Le four continue son petit bruit. La fenêtre reste embuée. Raphaël dessine un petit rond dans la buée. Un rond, c'est joli. Mila dessine un soleil à côté. On a le souvenir. Oui. Le gâteau cuit tout doucement. La cuisine est chaude et douce. Mila pose sa joue sur la table. Le bois est un peu collant. Tu veux un verre d'eau ? Oui, maman. L'eau est fraîche. Elle fait un petit cloc dans le verre. Et le téléphone est avec toi. Oui. Une goutte de vanille brille sur la cuillère. Mila la montre du doigt. C'est sucré. Oui. On goûtera le gâteau plus tard. Le four fait toujours son petit bruit.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1342,44 +1342,41 @@
 enfant-m|Mila, tu as de la farine.
 narrateur|Mila se touche le nez.
 narrateur|Elle rit un peu.
+enfant-m|Je veux un souvenir.
 narrateur|Raphaël voit le téléphone de maman.
 narrateur|Le téléphone est sur la table.
 narrateur|Il est loin de la pâte.
-enfant-m|Je peux prendre une photo ?
-maman|On doit demander.
-maman|Demander, c'est parler avant.
-maman|Une photo se fait avec un adulte.
-maman|Le téléphone reste avec l'adulte.
-maman|Ce n'est pas pour rire de l'autre.
-enfant-m|D'accord.
+narrateur|Raphaël avance la main.
+narrateur|Maman ne bouge pas.
+narrateur|Maman attend, tout près.
+narrateur|Raphaël pose sa main.
+enfant-m|Maman, je peux demander une photo ?
+maman|Oui.
 narrateur|Raphaël se tourne vers Mila.
 enfant-m|Mila, on peut ?
-narrateur|Mila dit oui.
-narrateur|Mila essuie son nez.
-maman|Bravo, Raphaël.
-maman|Tu as demandé.
+copine|Oui.
+narrateur|Mila essuie un peu son nez.
+narrateur|Un point blanc reste.
 narrateur|Maman prend le téléphone.
 narrateur|Le téléphone reste dans sa main.
 narrateur|Maman prend la photo.
 narrateur|Raphaël et Mila sourient.
 enfant-m|Merci, maman.
-maman|De rien.
+maman|Bravo, Raphaël.
 narrateur|Le saladier brille encore.
 narrateur|Le gâteau sent plus fort.
+narrateur|Plus tard, le four s'ouvre.
+narrateur|Le gâteau est doré, tout chaud.
 enfant-m|Et le gâteau ?
-enfant-m|On peut une photo du gâteau ?
-maman|On demande encore.
-maman|Le téléphone reste avec moi.
+enfant-m|Un souvenir du gâteau ?
+narrateur|Raphaël avance encore la main.
+narrateur|Maman attend encore.
 enfant-m|On peut, maman ?
 maman|Oui.
 narrateur|Maman photographie le gâteau doré.
-narrateur|Ce n'est pas pour rire de l'autre.
-narrateur|C'est pour garder le moment.
-maman|Tu as demandé deux fois.
-maman|Bravo.
+narrateur|Le téléphone reste avec elle.
 enfant-m|Le téléphone est avec toi.
 maman|Oui.
-maman|Avec l'adulte.
 narrateur|Ils lèchent un peu de pâte.
 narrateur|C'est sucré et doux.
 maman|Tu as fini de mélanger ?
@@ -1389,12 +1386,8 @@
 narrateur|Raphaël dessine un petit rond dans la buée.
 maman|Un rond, c'est joli.
 narrateur|Mila dessine un soleil à côté.
-maman|Vous avez demandé avant la photo.
-maman|C'est le bon geste.
-enfant-m|On demande.
-enfant-m|L'adulte a le téléphone.
+enfant-m|On a le souvenir.
 maman|Oui.
-maman|Pas pour rire de l'autre.
 narrateur|Le gâteau cuit tout doucement.
 narrateur|La cuisine est chaude et douce.
 narrateur|Mila pose sa joue sur la table.
@@ -1403,7 +1396,6 @@
 enfant-m|Oui, maman.
 narrateur|L'eau est fraîche.
 narrateur|Elle fait un petit cloc dans le verre.
-maman|On a demandé avant la photo.
 enfant-m|Et le téléphone est avec toi.
 maman|Oui.
 narrateur|Une goutte de vanille brille sur la cuillère.
@@ -1463,7 +1455,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>demander | à maman | adulte | demander à l'adulte</t>
+          <t>demander | à maman | adulte | demander à l'adulte | je peux</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1478,7 +1470,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>On demande à l'adulte. Ce n'est pas pour rire de l'autre. Que fait Quentin ?</t>
+          <t>Raphaël parle à maman. Que fait-il ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1527,7 +1519,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1627,12 +1619,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a su demander. Le téléphone reste avec l'adulte. Ce n'est pas pour rire de l'autre. Bravo, Raphaël. J'ai demandé. Le téléphone est avec toi. Oui. Avec l'adulte. On demande avant une photo.</t>
+          <t>Raphaël a parlé à maman. Alors les photos sont arrivées. Le téléphone est resté avec elle. Bravo, Raphaël. J'ai parlé. Le téléphone est avec toi. Oui. Avec moi.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a su demander. Le téléphone reste avec l'adulte. Ce n'est pas pour rire de l'autre. Bravo, Raphaël. J'ai demandé. Le téléphone est avec toi. Oui. Avec l'adulte. On demande avant une photo.</t>
+          <t>Raphaël a parlé à maman. Alors les photos sont arrivées. Le téléphone est resté avec elle. Bravo, Raphaël. J'ai parlé. Le téléphone est avec toi. Oui. Avec moi.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1695,7 +1687,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1771,15 +1763,14 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël a su demander.
-narrateur|Le téléphone reste avec l'adulte.
-narrateur|Ce n'est pas pour rire de l'autre.
+          <t>narrateur|Raphaël a parlé à maman.
+narrateur|Alors les photos sont arrivées.
+narrateur|Le téléphone est resté avec elle.
 maman|Bravo, Raphaël.
-enfant-m|J'ai demandé.
+enfant-m|J'ai parlé.
 enfant-m|Le téléphone est avec toi.
 maman|Oui.
-maman|Avec l'adulte.
-maman|On demande avant une photo.</t>
+maman|Avec moi.</t>
         </is>
       </c>
     </row>
@@ -1806,12 +1797,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Raphaël et Mila rangent le saladier. La cuillère tapote encore un peu. Tu glisses le saladier ici ? Oui, maman. Maman range le téléphone. Il n'est plus sur la table. On attend le gâteau, maintenant. Il sent bon. Oui. Tu as demandé. C'était le bon geste. La buée part tout doucement. Un rond reste sur la vitre.</t>
+          <t>Raphaël et Mila rangent le saladier. La cuillère tapote encore un peu. Tu glisses le saladier ici ? Oui, maman. Maman range le téléphone. Il n'est plus sur la table. On attend le gâteau, maintenant. Il sent bon. Oui. La buée part tout doucement. Un rond reste sur la vitre.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Raphaël et Mila rangent le saladier. La cuillère tapote encore un peu. Tu glisses le saladier ici ? Oui, maman. Maman range le téléphone. Il n'est plus sur la table. On attend le gâteau, maintenant. Il sent bon. Oui. Tu as demandé. C'était le bon geste. La buée part tout doucement. Un rond reste sur la vitre.</t>
+          <t>Raphaël et Mila rangent le saladier. La cuillère tapote encore un peu. Tu glisses le saladier ici ? Oui, maman. Maman range le téléphone. Il n'est plus sur la table. On attend le gâteau, maintenant. Il sent bon. Oui. La buée part tout doucement. Un rond reste sur la vitre.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1874,7 +1865,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1951,8 +1942,6 @@
 maman|On attend le gâteau, maintenant.
 enfant-m|Il sent bon.
 maman|Oui.
-maman|Tu as demandé.
-maman|C'était le bon geste.
 narrateur|La buée part tout doucement.
 narrateur|Un rond reste sur la vitre.</t>
         </is>
@@ -1981,12 +1970,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>On a demandé. Le téléphone est avec maman. Bravo. Le gâteau cuit encore. La cuisine sent la vanille.</t>
+          <t>On a un souvenir. Le téléphone est avec maman. Bravo. Le gâteau cuit encore. La cuisine sent la vanille.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>On a demandé. Le téléphone est avec maman. Bravo. Le gâteau cuit encore. La cuisine sent la vanille.</t>
+          <t>On a un souvenir. Le téléphone est avec maman. Bravo. Le gâteau cuit encore. La cuisine sent la vanille.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2042,14 +2031,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2121,7 +2110,7 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-m|On a demandé.
+          <t>enfant-m|On a un souvenir.
 enfant-m|Le téléphone est avec maman.
 maman|Bravo.
 narrateur|Le gâteau cuit encore.
@@ -2146,7 +2135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2196,6 +2185,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
